--- a/artfynd/A 13038-2024 artfynd.xlsx
+++ b/artfynd/A 13038-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94956417</v>
+        <v>94891760</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -713,32 +708,24 @@
           <t>25</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jakttornet, knärot, Myra 300 m sso, Srm</t>
+          <t>jakttornet rätt, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>617665.6040883972</v>
+        <v>617680</v>
       </c>
       <c r="R2" t="n">
-        <v>6525758.401221838</v>
+        <v>6525815</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -763,34 +750,19 @@
           <t>Runtuna</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>D-Nyk-0492</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>25 blomstänglar, troiigen 100 skott. Hot föreligger!</t>
+          <t>liten starkt hotad lokal</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -808,15 +780,10 @@
           <t>Skogsmark</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Gunilla Björkhem</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -824,23 +791,14 @@
           <t>Gunilla Björkhem</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94891760</v>
+        <v>94956417</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -870,24 +828,32 @@
           <t>25</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>jakttornet rätt, Srm</t>
+          <t>Jakttornet, knärot, Myra 300 m sso, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617680</v>
+        <v>617666</v>
       </c>
       <c r="R3" t="n">
-        <v>6525815</v>
+        <v>6525759</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -912,6 +878,11 @@
           <t>Runtuna</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>D-Nyk-0492</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
           <t>2021-07-12</t>
@@ -924,7 +895,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>liten starkt hotad lokal</t>
+          <t>25 blomstänglar, troiigen 100 skott. Hot föreligger!</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -942,18 +913,27 @@
           <t>Skogsmark</t>
         </is>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
           <t>Gunilla Björkhem</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Gunilla Björkhem</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13038-2024 artfynd.xlsx
+++ b/artfynd/A 13038-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94891760</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -934,8 +944,17 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94956417</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>